--- a/templates/preortho_order_list.xlsx
+++ b/templates/preortho_order_list.xlsx
@@ -762,6 +762,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="13" customWidth="1" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
